--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCP.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,83 +590,83 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>36</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>21</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="n">
         <v>9</v>
       </c>
-      <c r="T2" t="n">
-        <v>11</v>
-      </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
         <v>8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>SCP_J._DAVIS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Davis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +928,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: 0 (18 L)</t>
+          <t>Maior volume: Liam Reilly (27 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +940,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: 0 (7 3PA)</t>
+          <t>Maior volume 3pt: Liam Reilly (12 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +952,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: 0 (1.2 pts/shot)</t>
+          <t>Mais eficaz: B. Carter (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +964,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (21 L)</t>
+          <t>Zona mais usada: Restricted Area (36 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +976,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (63.6%)</t>
+          <t>Zona mais eficaz: Restricted Area (66.7%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -928,43 +1116,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_0</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -972,31 +1160,31 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1005,75 +1193,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1082,47 +1270,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1130,89 +1318,93 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
       <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
         <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1223,73 +1415,69 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1300,80 +1488,84 @@
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1382,35 +1574,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1418,97 +1614,97 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
         <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1516,47 +1712,47 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
       <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1564,11 +1760,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1576,11 +1772,11 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1600,69 +1796,73 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_J._EMBALO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1673,14 +1873,148 @@
         <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCP_J._GOMES</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>J. Gomes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11</v>
+      </c>
+      <c r="S12" t="n">
         <v>7</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCP_M._BOWMAN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M. Bowman</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1691,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1707,7 +2041,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -1815,12 +2149,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_0</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1828,223 +2162,525 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>38.9%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCP_T._BASKIN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="S4" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>2</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>47.8%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2055,7 +2691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2149,38 +2785,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_0</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2188,11 +2824,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2205,50 +2841,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2261,42 +2897,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2304,14 +2940,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2326,29 +2962,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2356,18 +2992,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2382,41 +3018,41 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -2438,29 +3074,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -2468,18 +3104,18 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2494,75 +3130,85 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2574,49 +3220,55 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._GOMES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2624,66 +3276,180 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>7</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCP_M._BOWMAN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M. Bowman</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCP_J._DAVIS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Davis</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N11"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2694,28 +3460,267 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>47.8%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2790,176 +3795,176 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2969,7 +3974,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -2987,7 +3992,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3009,7 +4014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3020,7 +4025,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3115,12 +4120,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_0</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3129,143 +4134,143 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3273,29 +4278,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3303,65 +4308,65 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -3373,52 +4378,56 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3429,34 +4438,30 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3465,11 +4470,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3478,84 +4483,112 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
       <c r="P8" t="n">
         <v>0.7</v>
       </c>
@@ -3563,82 +4596,82 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3647,11 +4680,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3667,87 +4700,211 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_J._EMBALO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCP_J._GOMES</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>J. Gomes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>1</v>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCP_M._BOWMAN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M. Bowman</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3758,7 +4915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3834,12 +4991,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_0</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3848,25 +5005,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -3893,81 +5050,396 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_0</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCP_T._BASKIN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H10" t="n">
         <v>1.2</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCP.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
         <v>9</v>
@@ -663,10 +663,10 @@
         <v>9</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,76 +802,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -889,8 +889,188 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40.5%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCP_J._DAVIS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Davis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -928,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: Liam Reilly (27 L)</t>
+          <t>Maior volume: Liam Reilly (37 L)</t>
         </is>
       </c>
     </row>
@@ -940,7 +1120,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: Liam Reilly (12 3PA)</t>
+          <t>Maior volume 3pt: Liam Reilly (18 3PA)</t>
         </is>
       </c>
     </row>
@@ -952,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: B. Carter (1.2 pts/shot)</t>
+          <t>Mais eficaz: Liam Reilly (1.1 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -964,7 +1144,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (36 L)</t>
+          <t>Zona mais usada: Restricted Area (57 L)</t>
         </is>
       </c>
     </row>
@@ -1125,30 +1305,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>45.9%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1160,7 +1340,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1173,18 +1353,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1202,30 +1382,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1237,31 +1417,31 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1279,66 +1459,66 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>48.3%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="E4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>36.8%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>52.6%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1347,43 +1527,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1391,11 +1567,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1404,94 +1580,98 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
         <v>8</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -1506,17 +1686,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1529,11 +1709,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1541,11 +1721,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1562,72 +1742,72 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1635,80 +1815,80 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1719,10 +1899,10 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1737,7 +1917,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -1747,7 +1927,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1760,11 +1940,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1772,20 +1952,20 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1796,10 +1976,10 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1814,7 +1994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1824,41 +2004,41 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1866,14 +2046,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1882,16 +2062,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_J._GOMES</t>
+          <t>SCP_G._TEIXEIRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>G. Teixeira</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1905,7 +2085,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1922,7 +2102,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1933,14 +2113,24 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -1958,59 +2148,69 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>12</v>
       </c>
       <c r="R13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" t="n">
         <v>11</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2025,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2041,7 +2241,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2149,55 +2349,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2206,103 +2406,109 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
       <c r="R3" t="n">
-        <v>4</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2310,42 +2516,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2354,53 +2556,51 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2409,12 +2609,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -2422,225 +2622,225 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>60.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2649,11 +2849,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2662,25 +2862,102 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2794,26 +3071,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
         <v>1.1</v>
@@ -2824,7 +3101,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -2850,26 +3127,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
         <v>0.9</v>
@@ -2880,18 +3157,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2906,29 +3183,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2936,18 +3213,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2962,48 +3239,48 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3018,41 +3295,41 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -3074,29 +3351,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3104,11 +3381,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -3121,16 +3398,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_G._TEIXEIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>G. Teixeira</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3142,47 +3419,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3198,47 +3475,47 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
         <v>6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_J._GOMES</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3254,33 +3531,33 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
         <v>7</v>
@@ -3289,16 +3566,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._GOMES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3310,47 +3587,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_M._BOWMAN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M. Bowman</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3366,69 +3643,73 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_M._BOWMAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>M. Bowman</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -3436,17 +3717,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -3460,7 +3743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3563,26 +3846,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
         <v>1.1</v>
@@ -3593,7 +3876,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -3610,54 +3893,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -3666,61 +3949,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
         <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3799,13 +4138,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3817,7 +4156,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3834,29 +4173,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -3869,25 +4208,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3900,71 +4239,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
-        <v>24</v>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3974,25 +4313,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4134,7 +4473,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4147,11 +4486,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4160,27 +4499,27 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>45.9%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4204,53 +4543,53 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="L3" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -4274,68 +4613,68 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4344,11 +4683,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4357,100 +4696,100 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
       <c r="L6" t="n">
+        <v>17</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>10</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -4470,11 +4809,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4504,11 +4843,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -4520,36 +4859,36 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4557,84 +4896,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
@@ -4644,23 +4983,23 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -4680,45 +5019,45 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -4730,7 +5069,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -4746,20 +5085,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4767,56 +5106,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_J._GOMES</t>
+          <t>SCP_G._TEIXEIRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>G. Teixeira</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4827,14 +5166,24 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4842,7 +5191,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -4866,41 +5215,51 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4915,7 +5274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5005,13 +5364,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5023,104 +5382,104 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -5140,7 +5499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -5150,15 +5509,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -5185,25 +5544,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5216,43 +5575,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -5261,111 +5620,111 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -5375,71 +5734,341 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCP_A._CRUZ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A. Cruz</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17.2%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCP_B._CARTER</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B. Carter</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCP.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>142</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>47.2%</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>114</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>82</v>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,44 +629,44 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>77</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>26.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>57</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -847,12 +847,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -871,109 +871,109 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -982,95 +982,275 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCP_J._DAVIS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Davis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>27.6%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>SCP_D._VENTURA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>D. Ventura</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60.9%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1108,7 +1288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: Liam Reilly (37 L)</t>
+          <t>Maior volume: Liam Reilly (49 L)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1300,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: Liam Reilly (18 3PA)</t>
+          <t>Maior volume 3pt: Liam Reilly (26 3PA)</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: Liam Reilly (1.1 pts/shot)</t>
+          <t>Mais eficaz: J. Davis (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1324,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (57 L)</t>
+          <t>Zona mais usada: Above the Break 3 (77 L)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1336,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (66.7%)</t>
+          <t>Zona mais eficaz: Restricted Area (61.3%)</t>
         </is>
       </c>
     </row>
@@ -1305,34 +1485,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1340,11 +1520,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1353,18 +1533,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1382,30 +1562,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>35.3%</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1417,11 +1597,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1430,18 +1610,18 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1459,34 +1639,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1494,11 +1674,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1507,18 +1687,18 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1536,17 +1716,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1559,7 +1739,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1567,7 +1747,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1591,7 +1771,7 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>13</v>
@@ -1609,34 +1789,34 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
         <v>17</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1644,11 +1824,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1657,11 +1837,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1677,55 +1857,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>8</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1734,63 +1914,63 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1798,16 +1978,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1822,129 +2002,129 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._EMBALO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>54.5%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
         <v>5</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1952,7 +2132,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1961,7 +2141,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1969,55 +2149,55 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2025,84 +2205,84 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_G._TEIXEIRA</t>
+          <t>SCP_M._BOWMAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Teixeira</t>
+          <t>M. Bowman</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2110,7 +2290,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2123,76 +2303,76 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCP_M._BOWMAN</t>
+          <t>SCP_G._TEIXEIRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M. Bowman</t>
+          <t>G. Teixeira</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2207,10 +2387,10 @@
         <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2225,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2349,55 +2529,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2406,32 +2582,30 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2439,115 +2613,119 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2560,243 +2738,245 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>18</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -2805,12 +2985,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2818,65 +2998,65 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
         <v>12</v>
       </c>
-      <c r="G8" t="n">
-        <v>30</v>
-      </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2891,33 +3071,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="E9" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
         <v>17</v>
       </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11</v>
-      </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2926,11 +3106,11 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2939,11 +3119,11 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2956,8 +3136,85 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCP_J._EMBALO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3071,29 +3328,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3101,18 +3358,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3127,26 +3384,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I3" t="n">
         <v>0.9</v>
@@ -3157,18 +3414,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3183,29 +3440,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3213,18 +3470,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3239,29 +3496,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="n">
         <v>17</v>
       </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3269,11 +3526,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -3295,29 +3552,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3325,7 +3582,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3336,7 +3593,7 @@
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3392,7 +3649,7 @@
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3448,44 +3705,44 @@
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_M._BOWMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>M. Bowman</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3493,29 +3750,29 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3531,29 +3788,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>8</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3566,12 +3823,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_J._GOMES</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3587,51 +3844,51 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._GOMES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -3643,47 +3900,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCP_M._BOWMAN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M. Bowman</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3699,17 +3956,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -3717,15 +3974,15 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
@@ -3743,7 +4000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3846,29 +4103,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3876,127 +4133,127 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
@@ -4014,29 +4271,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="n">
         <v>17</v>
       </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4044,11 +4301,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4058,8 +4315,64 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCP_J._EMBALO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4134,71 +4447,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4208,25 +4521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4239,71 +4552,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -4313,25 +4626,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4473,11 +4786,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4486,11 +4799,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4499,31 +4812,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4543,11 +4856,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4556,11 +4869,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4569,27 +4882,27 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>24</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>37.5%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>17</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>35.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -4613,11 +4926,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4626,44 +4939,44 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4683,7 +4996,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4707,11 +5020,11 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -4719,7 +5032,7 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -4739,11 +5052,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4752,11 +5065,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4773,34 +5086,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4809,11 +5122,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4822,16 +5135,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4843,15 +5156,15 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -4859,18 +5172,18 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4879,16 +5192,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4901,81 +5214,81 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_J._EMBALO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4983,34 +5296,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5019,7 +5332,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5028,7 +5341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5036,106 +5349,106 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>14.3%</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -5145,17 +5458,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_G._TEIXEIRA</t>
+          <t>SCP_M._BOWMAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Teixeira</t>
+          <t>M. Bowman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5163,72 +5476,82 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCP_M._BOWMAN</t>
+          <t>SCP_G._TEIXEIRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M. Bowman</t>
+          <t>G. Teixeira</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -5243,15 +5566,15 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -5259,7 +5582,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5274,7 +5597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5350,91 +5673,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
         <v>15</v>
       </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5454,25 +5777,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5499,25 +5822,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -5544,7 +5867,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -5554,157 +5877,157 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5720,74 +6043,74 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -5800,57 +6123,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5859,32 +6182,32 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5904,7 +6227,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -5914,22 +6237,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5949,7 +6272,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -5959,22 +6282,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5994,7 +6317,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -6004,71 +6327,206 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SCP_A._CRUZ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A. Cruz</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SCP_J._EMBALO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>SCP_B._CARTER</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>B. Carter</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H20" t="n">
         <v>0.8</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>